--- a/Assets/@Resources/Data/Excel/SpeedPotionData.xlsx
+++ b/Assets/@Resources/Data/Excel/SpeedPotionData.xlsx
@@ -611,8 +611,10 @@
           <t>SPDPotion1NameText</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -661,8 +663,10 @@
           <t>SPDPotion1NameText</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -711,8 +715,10 @@
           <t>SPDPotion1NameText</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -761,8 +767,10 @@
           <t>SPDPotion2NameText</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>1</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/Assets/@Resources/Data/Excel/SpeedPotionData.xlsx
+++ b/Assets/@Resources/Data/Excel/SpeedPotionData.xlsx
@@ -611,10 +611,8 @@
           <t>SPDPotion1NameText</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
+      <c r="C4" t="n">
+        <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -663,10 +661,8 @@
           <t>SPDPotion1NameText</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
+      <c r="C5" t="n">
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -715,10 +711,8 @@
           <t>SPDPotion1NameText</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
+      <c r="C6" t="n">
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -767,10 +761,8 @@
           <t>SPDPotion2NameText</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Abnormal</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
